--- a/fuentes/comparativa_reg_retributivo.xlsx
+++ b/fuentes/comparativa_reg_retributivo.xlsx
@@ -1531,7 +1531,7 @@
     <t>Umbral revisar: 1 EUR; umbral diferencia: 50 EUR.</t>
   </si>
   <si>
-    <t>IA desactivada; justificaciones deterministas.</t>
+    <t>Gemini solo puede sugerir textos y mapeos, nunca calcular importes.</t>
   </si>
   <si>
     <t>Hoja Registro detectada: Empleados.</t>
